--- a/results/detailedWER.xlsx
+++ b/results/detailedWER.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="1767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1856" uniqueCount="1767">
   <si>
     <t xml:space="preserve">Sentence number</t>
   </si>
@@ -5369,7 +5369,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -5393,6 +5393,14 @@
       <family val="0"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
@@ -5485,7 +5493,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5506,8 +5514,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -5518,7 +5530,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5599,7 +5615,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
+  <dimension ref="A1:Q1000"/>
   <sheetFormatPr defaultColWidth="11.1640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.5"/>
@@ -5613,10 +5629,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="29.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="40.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="25.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="26.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="30.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="14" style="1" width="10.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="31" style="1" width="11.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="26.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="30.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="17.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="17" style="1" width="10.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="33" style="1" width="11.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="39.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5653,11 +5670,20 @@
       <c r="K1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>5</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5694,11 +5720,20 @@
       <c r="K2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>14</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5735,11 +5770,20 @@
       <c r="K3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="N3" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O3" s="4" t="s">
         <v>22</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5776,11 +5820,20 @@
       <c r="K4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="N4" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O4" s="4" t="s">
         <v>30</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5817,11 +5870,20 @@
       <c r="K5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="4" t="s">
-        <v>37</v>
+      <c r="L5" s="1" t="n">
+        <v>0.4</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>37</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5858,11 +5920,20 @@
       <c r="K6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="N6" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O6" s="4" t="s">
         <v>44</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5899,11 +5970,20 @@
       <c r="K7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="N7" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O7" s="4" t="s">
         <v>52</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5940,11 +6020,20 @@
       <c r="K8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M8" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="N8" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O8" s="4" t="s">
         <v>59</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5981,11 +6070,20 @@
       <c r="K9" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M9" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="N9" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O9" s="4" t="s">
         <v>66</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6022,11 +6120,20 @@
       <c r="K10" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4" t="s">
         <v>73</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6063,11 +6170,20 @@
       <c r="K11" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="1" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="M11" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="N11" s="4" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="O11" s="4" t="s">
         <v>81</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6104,11 +6220,20 @@
       <c r="K12" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="L12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="N12" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O12" s="4" t="s">
         <v>89</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6145,11 +6270,20 @@
       <c r="K13" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="L13" s="4" t="s">
-        <v>96</v>
+      <c r="L13" s="1" t="n">
+        <v>0.2</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>96</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6186,11 +6320,20 @@
       <c r="K14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="L14" s="4" t="s">
-        <v>103</v>
+      <c r="L14" s="1" t="n">
+        <v>0.2</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>103</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6227,11 +6370,20 @@
       <c r="K15" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="L15" s="1" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="M15" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="N15" s="4" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="O15" s="4" t="s">
         <v>111</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6268,14 +6420,22 @@
       <c r="K16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="L16" s="4" t="s">
+      <c r="L16" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M16" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="M16" s="4" t="s">
+      <c r="N16" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O16" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
+      <c r="P16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
@@ -6311,14 +6471,22 @@
       <c r="K17" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="L17" s="4" t="s">
+      <c r="L17" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M17" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="M17" s="4" t="s">
+      <c r="N17" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O17" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
+      <c r="P17" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
@@ -6354,14 +6522,22 @@
       <c r="K18" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="L18" s="4" t="s">
+      <c r="L18" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M18" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="M18" s="4" t="s">
+      <c r="N18" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O18" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
+      <c r="P18" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
@@ -6397,14 +6573,22 @@
       <c r="K19" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="L19" s="4" t="s">
+      <c r="L19" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M19" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="M19" s="4" t="s">
+      <c r="N19" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O19" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
+      <c r="P19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
@@ -6440,14 +6624,22 @@
       <c r="K20" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="L20" s="4" t="s">
+      <c r="L20" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M20" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="M20" s="4" t="s">
+      <c r="N20" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O20" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
+      <c r="P20" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -6483,14 +6675,22 @@
       <c r="K21" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="L21" s="4" t="s">
+      <c r="L21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="M21" s="4" t="s">
+      <c r="N21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
+      <c r="P21" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
@@ -6526,14 +6726,22 @@
       <c r="K22" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="L22" s="4" t="s">
+      <c r="L22" s="1" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="M22" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="M22" s="4" t="s">
+      <c r="N22" s="4" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="O22" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
+      <c r="P22" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
@@ -6569,14 +6777,22 @@
       <c r="K23" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="L23" s="4" t="s">
+      <c r="L23" s="1" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="M23" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="M23" s="4" t="s">
+      <c r="N23" s="4" t="n">
+        <v>1.16666666666667</v>
+      </c>
+      <c r="O23" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
+      <c r="P23" s="6" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="Q23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
@@ -6612,14 +6828,22 @@
       <c r="K24" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="L24" s="4" t="s">
+      <c r="L24" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M24" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="M24" s="4" t="s">
+      <c r="N24" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O24" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
+      <c r="P24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
@@ -6655,14 +6879,22 @@
       <c r="K25" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="L25" s="4" t="s">
+      <c r="L25" s="1" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="M25" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="M25" s="4" t="s">
+      <c r="N25" s="4" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="O25" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
+      <c r="P25" s="6" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="Q25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
@@ -6698,14 +6930,22 @@
       <c r="K26" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="L26" s="4" t="s">
+      <c r="L26" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M26" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="M26" s="4" t="s">
+      <c r="N26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
+      <c r="P26" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
@@ -6741,14 +6981,22 @@
       <c r="K27" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="L27" s="4" t="s">
+      <c r="L27" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M27" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="M27" s="4" t="s">
+      <c r="N27" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O27" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
+      <c r="P27" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q27" s="6"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
@@ -6784,14 +7032,22 @@
       <c r="K28" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L28" s="4" t="s">
+      <c r="L28" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M28" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="M28" s="4" t="s">
+      <c r="N28" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O28" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
+      <c r="P28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
@@ -6827,14 +7083,22 @@
       <c r="K29" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="L29" s="4" t="s">
+      <c r="L29" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M29" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="M29" s="4" t="s">
+      <c r="N29" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O29" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
+      <c r="P29" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q29" s="6"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
@@ -6870,14 +7134,22 @@
       <c r="K30" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="L30" s="4" t="s">
+      <c r="L30" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M30" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="M30" s="4" t="s">
+      <c r="N30" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O30" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
+      <c r="P30" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q30" s="6"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
@@ -6913,14 +7185,22 @@
       <c r="K31" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="L31" s="4" t="s">
-        <v>236</v>
+      <c r="L31" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5"/>
+      <c r="N31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
@@ -6956,14 +7236,22 @@
       <c r="K32" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="L32" s="4" t="s">
+      <c r="L32" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M32" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="M32" s="4" t="s">
+      <c r="N32" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O32" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5"/>
+      <c r="P32" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
@@ -6999,14 +7287,22 @@
       <c r="K33" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="L33" s="4" t="s">
+      <c r="L33" s="1" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="M33" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="M33" s="4" t="s">
+      <c r="N33" s="4" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="O33" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
+      <c r="P33" s="6" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="Q33" s="6"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
@@ -7042,14 +7338,22 @@
       <c r="K34" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="L34" s="4" t="s">
+      <c r="L34" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M34" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="M34" s="4" t="s">
+      <c r="N34" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O34" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5"/>
+      <c r="P34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
@@ -7085,14 +7389,22 @@
       <c r="K35" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="L35" s="4" t="s">
+      <c r="L35" s="1" t="n">
+        <v>1.33333333333333</v>
+      </c>
+      <c r="M35" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="M35" s="4" t="s">
+      <c r="N35" s="4" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="O35" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5"/>
+      <c r="P35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
@@ -7107,10 +7419,10 @@
       <c r="D36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="8" t="n">
         <v>0.333333333333333</v>
       </c>
       <c r="G36" s="1" t="s">
@@ -7128,14 +7440,22 @@
       <c r="K36" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="L36" s="4" t="s">
+      <c r="L36" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M36" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="M36" s="4" t="s">
+      <c r="N36" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O36" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
+      <c r="P36" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="n">
@@ -7171,14 +7491,22 @@
       <c r="K37" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="L37" s="4" t="s">
+      <c r="L37" s="1" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="M37" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="M37" s="4" t="s">
+      <c r="N37" s="4" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="O37" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5"/>
+      <c r="P37" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
@@ -7214,14 +7542,22 @@
       <c r="K38" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="L38" s="4" t="s">
+      <c r="L38" s="1" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="M38" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="M38" s="4" t="s">
+      <c r="N38" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O38" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
+      <c r="P38" s="6" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="Q38" s="6"/>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
@@ -7257,14 +7593,22 @@
       <c r="K39" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="L39" s="4" t="s">
-        <v>298</v>
+      <c r="L39" s="1" t="n">
+        <v>0.4</v>
       </c>
       <c r="M39" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="N39" s="5"/>
-      <c r="O39" s="5"/>
+      <c r="N39" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O39" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="n">
@@ -7300,14 +7644,22 @@
       <c r="K40" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="L40" s="4" t="s">
+      <c r="L40" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M40" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="M40" s="4" t="s">
+      <c r="N40" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O40" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
+      <c r="P40" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q40" s="6"/>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="n">
@@ -7343,14 +7695,22 @@
       <c r="K41" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="L41" s="4" t="s">
+      <c r="L41" s="1" t="n">
+        <v>0.714285714285714</v>
+      </c>
+      <c r="M41" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="M41" s="4" t="s">
+      <c r="N41" s="4" t="n">
+        <v>0.714285714285714</v>
+      </c>
+      <c r="O41" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5"/>
+      <c r="P41" s="6" t="n">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="Q41" s="6"/>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
@@ -7386,14 +7746,22 @@
       <c r="K42" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="L42" s="4" t="s">
+      <c r="L42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="M42" s="4" t="s">
+      <c r="N42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5"/>
+      <c r="P42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="6"/>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="n">
@@ -7429,14 +7797,22 @@
       <c r="K43" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="L43" s="4" t="s">
+      <c r="L43" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M43" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="M43" s="4" t="s">
+      <c r="N43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5"/>
+      <c r="P43" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="n">
@@ -7472,14 +7848,22 @@
       <c r="K44" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="L44" s="4" t="s">
+      <c r="L44" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M44" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="M44" s="4" t="s">
+      <c r="N44" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O44" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5"/>
+      <c r="P44" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q44" s="6"/>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="n">
@@ -7515,14 +7899,22 @@
       <c r="K45" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="L45" s="4" t="s">
+      <c r="L45" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M45" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="M45" s="4" t="s">
+      <c r="N45" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O45" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="N45" s="5"/>
-      <c r="O45" s="5"/>
+      <c r="P45" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="n">
@@ -7558,14 +7950,22 @@
       <c r="K46" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="L46" s="4" t="s">
+      <c r="L46" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M46" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="M46" s="4" t="s">
+      <c r="N46" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O46" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5"/>
+      <c r="P46" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q46" s="6"/>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="n">
@@ -7601,14 +8001,22 @@
       <c r="K47" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="L47" s="4" t="s">
+      <c r="L47" s="1" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="M47" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="M47" s="4" t="s">
+      <c r="N47" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O47" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="N47" s="5"/>
-      <c r="O47" s="5"/>
+      <c r="P47" s="6" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="Q47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="n">
@@ -7644,14 +8052,22 @@
       <c r="K48" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="L48" s="4" t="s">
+      <c r="L48" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M48" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="M48" s="4" t="s">
+      <c r="N48" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O48" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="N48" s="5"/>
-      <c r="O48" s="5"/>
+      <c r="P48" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q48" s="6"/>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="n">
@@ -7687,14 +8103,22 @@
       <c r="K49" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="L49" s="4" t="s">
+      <c r="L49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="M49" s="4" t="s">
+      <c r="N49" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O49" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="N49" s="5"/>
-      <c r="O49" s="5"/>
+      <c r="P49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="6"/>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="n">
@@ -7730,14 +8154,22 @@
       <c r="K50" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="L50" s="4" t="s">
+      <c r="L50" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M50" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="M50" s="4" t="s">
+      <c r="N50" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O50" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="N50" s="5"/>
-      <c r="O50" s="5"/>
+      <c r="P50" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q50" s="6"/>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="n">
@@ -7773,14 +8205,22 @@
       <c r="K51" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="L51" s="4" t="s">
-        <v>388</v>
+      <c r="L51" s="1" t="n">
+        <v>0.4</v>
       </c>
       <c r="M51" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="N51" s="5"/>
-      <c r="O51" s="5"/>
+      <c r="N51" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O51" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q51" s="6"/>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="n">
@@ -7816,14 +8256,22 @@
       <c r="K52" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L52" s="4" t="s">
+      <c r="L52" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M52" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="M52" s="4" t="s">
+      <c r="N52" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O52" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="N52" s="5"/>
-      <c r="O52" s="5"/>
+      <c r="P52" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q52" s="6"/>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="n">
@@ -7859,14 +8307,22 @@
       <c r="K53" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="L53" s="4" t="s">
-        <v>401</v>
+      <c r="L53" s="1" t="n">
+        <v>0.2</v>
       </c>
       <c r="M53" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="N53" s="5"/>
-      <c r="O53" s="5"/>
+      <c r="N53" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O53" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q53" s="6"/>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="n">
@@ -7902,14 +8358,22 @@
       <c r="K54" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="L54" s="4" t="s">
-        <v>407</v>
+      <c r="L54" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="M54" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="N54" s="5"/>
-      <c r="O54" s="5"/>
+      <c r="N54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="6"/>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="n">
@@ -7945,14 +8409,22 @@
       <c r="K55" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="L55" s="4" t="s">
-        <v>414</v>
+      <c r="L55" s="1" t="n">
+        <v>0.6</v>
       </c>
       <c r="M55" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="N55" s="5"/>
-      <c r="O55" s="5"/>
+      <c r="N55" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O55" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="n">
@@ -7988,14 +8460,22 @@
       <c r="K56" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L56" s="4" t="s">
-        <v>421</v>
+      <c r="L56" s="1" t="n">
+        <v>0.4</v>
       </c>
       <c r="M56" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="N56" s="5"/>
-      <c r="O56" s="5"/>
+      <c r="N56" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O56" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q56" s="6"/>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="n">
@@ -8031,14 +8511,22 @@
       <c r="K57" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="L57" s="4" t="s">
+      <c r="L57" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M57" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="M57" s="4" t="s">
+      <c r="N57" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O57" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="N57" s="5"/>
-      <c r="O57" s="5"/>
+      <c r="P57" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q57" s="6"/>
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="n">
@@ -8074,14 +8562,22 @@
       <c r="K58" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L58" s="4" t="s">
+      <c r="L58" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M58" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="M58" s="4" t="s">
+      <c r="N58" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O58" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="N58" s="5"/>
-      <c r="O58" s="5"/>
+      <c r="P58" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q58" s="6"/>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="n">
@@ -8117,14 +8613,22 @@
       <c r="K59" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="L59" s="4" t="s">
+      <c r="L59" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M59" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="M59" s="4" t="s">
+      <c r="N59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="N59" s="5"/>
-      <c r="O59" s="5"/>
+      <c r="P59" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q59" s="6"/>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="n">
@@ -8160,14 +8664,22 @@
       <c r="K60" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="L60" s="4" t="s">
+      <c r="L60" s="1" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="M60" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="M60" s="4" t="s">
+      <c r="N60" s="4" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="O60" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="N60" s="5"/>
-      <c r="O60" s="5"/>
+      <c r="P60" s="6" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="Q60" s="6"/>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="n">
@@ -8203,14 +8715,22 @@
       <c r="K61" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="L61" s="4" t="s">
+      <c r="L61" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M61" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="M61" s="4" t="s">
+      <c r="N61" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O61" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="N61" s="5"/>
-      <c r="O61" s="5"/>
+      <c r="P61" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q61" s="6"/>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="n">
@@ -8237,9 +8757,20 @@
       <c r="H62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M62" s="5"/>
-      <c r="N62" s="5"/>
-      <c r="O62" s="5"/>
+      <c r="L62" s="9" t="n">
+        <f aca="false">SUM(L2:L61)/60</f>
+        <v>0.526904761904762</v>
+      </c>
+      <c r="N62" s="9" t="n">
+        <f aca="false">SUM(N2:N61)/60</f>
+        <v>0.506904761904762</v>
+      </c>
+      <c r="O62" s="6"/>
+      <c r="P62" s="9" t="n">
+        <f aca="false">SUM(P2:P61)/60</f>
+        <v>0.488174603174603</v>
+      </c>
+      <c r="Q62" s="6"/>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="n">
@@ -8266,9 +8797,9 @@
       <c r="H63" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M63" s="5"/>
-      <c r="N63" s="5"/>
-      <c r="O63" s="5"/>
+      <c r="O63" s="6"/>
+      <c r="P63" s="6"/>
+      <c r="Q63" s="6"/>
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="n">
@@ -8295,9 +8826,9 @@
       <c r="H64" s="2" t="n">
         <v>0.444444444444444</v>
       </c>
-      <c r="M64" s="5"/>
-      <c r="N64" s="5"/>
-      <c r="O64" s="5"/>
+      <c r="O64" s="6"/>
+      <c r="P64" s="6"/>
+      <c r="Q64" s="6"/>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="n">
@@ -8324,9 +8855,9 @@
       <c r="H65" s="2" t="n">
         <v>1.33333333333333</v>
       </c>
-      <c r="M65" s="5"/>
-      <c r="N65" s="5"/>
-      <c r="O65" s="5"/>
+      <c r="O65" s="6"/>
+      <c r="P65" s="6"/>
+      <c r="Q65" s="6"/>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="n">
@@ -8353,9 +8884,9 @@
       <c r="H66" s="2" t="n">
         <v>1.25</v>
       </c>
-      <c r="M66" s="5"/>
-      <c r="N66" s="5"/>
-      <c r="O66" s="5"/>
+      <c r="O66" s="6"/>
+      <c r="P66" s="6"/>
+      <c r="Q66" s="6"/>
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="n">
@@ -8382,9 +8913,9 @@
       <c r="H67" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="M67" s="5"/>
-      <c r="N67" s="5"/>
-      <c r="O67" s="5"/>
+      <c r="O67" s="6"/>
+      <c r="P67" s="6"/>
+      <c r="Q67" s="6"/>
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="n">
@@ -8411,9 +8942,9 @@
       <c r="H68" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="M68" s="5"/>
-      <c r="N68" s="5"/>
-      <c r="O68" s="5"/>
+      <c r="O68" s="6"/>
+      <c r="P68" s="6"/>
+      <c r="Q68" s="6"/>
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="n">
@@ -8440,9 +8971,9 @@
       <c r="H69" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="M69" s="5"/>
-      <c r="N69" s="5"/>
-      <c r="O69" s="5"/>
+      <c r="O69" s="6"/>
+      <c r="P69" s="6"/>
+      <c r="Q69" s="6"/>
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="n">
@@ -8469,9 +9000,9 @@
       <c r="H70" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M70" s="5"/>
-      <c r="N70" s="5"/>
-      <c r="O70" s="5"/>
+      <c r="O70" s="6"/>
+      <c r="P70" s="6"/>
+      <c r="Q70" s="6"/>
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="n">
@@ -8498,9 +9029,9 @@
       <c r="H71" s="2" t="n">
         <v>0.714285714285714</v>
       </c>
-      <c r="M71" s="5"/>
-      <c r="N71" s="5"/>
-      <c r="O71" s="5"/>
+      <c r="O71" s="6"/>
+      <c r="P71" s="6"/>
+      <c r="Q71" s="6"/>
     </row>
     <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="n">
@@ -8527,9 +9058,9 @@
       <c r="H72" s="2" t="n">
         <v>0.857142857142857</v>
       </c>
-      <c r="M72" s="5"/>
-      <c r="N72" s="5"/>
-      <c r="O72" s="5"/>
+      <c r="O72" s="6"/>
+      <c r="P72" s="6"/>
+      <c r="Q72" s="6"/>
     </row>
     <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="n">
@@ -8556,9 +9087,9 @@
       <c r="H73" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="M73" s="5"/>
-      <c r="N73" s="5"/>
-      <c r="O73" s="5"/>
+      <c r="O73" s="6"/>
+      <c r="P73" s="6"/>
+      <c r="Q73" s="6"/>
     </row>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="n">
@@ -8585,9 +9116,9 @@
       <c r="H74" s="2" t="n">
         <v>0.4</v>
       </c>
-      <c r="M74" s="5"/>
-      <c r="N74" s="5"/>
-      <c r="O74" s="5"/>
+      <c r="O74" s="6"/>
+      <c r="P74" s="6"/>
+      <c r="Q74" s="6"/>
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="n">
@@ -8614,9 +9145,9 @@
       <c r="H75" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="M75" s="5"/>
-      <c r="N75" s="5"/>
-      <c r="O75" s="5"/>
+      <c r="O75" s="6"/>
+      <c r="P75" s="6"/>
+      <c r="Q75" s="6"/>
     </row>
     <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="n">
@@ -17095,15 +17626,15 @@
       </c>
     </row>
     <row r="402" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D402" s="8" t="n">
+      <c r="D402" s="10" t="n">
         <f aca="false">SUM(D2:D401)/400</f>
         <v>0.648697312409812</v>
       </c>
-      <c r="F402" s="8" t="n">
+      <c r="F402" s="10" t="n">
         <f aca="false">SUM(F2:F401)/400</f>
         <v>0.585047741702742</v>
       </c>
-      <c r="H402" s="8" t="n">
+      <c r="H402" s="10" t="n">
         <f aca="false">SUM(H2:H401)/400</f>
         <v>0.630749025974026</v>
       </c>

--- a/results/detailedWER.xlsx
+++ b/results/detailedWER.xlsx
@@ -982,22 +982,22 @@
     <t xml:space="preserve">My shoulder feels softer tonight</t>
   </si>
   <si>
+    <t xml:space="preserve">My shirts dented in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i cant disagree with that</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I cant disagree with that</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I cant disagree with it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">please help cool my throat</t>
+  </si>
+  <si>
     <t xml:space="preserve">Please echo my flow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i cant disagree with that</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I cant disagree with that</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I cant disagree with it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">please help cool my throat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My shirts dented in</t>
   </si>
   <si>
     <t xml:space="preserve">Please a phone my flow</t>
@@ -7795,7 +7795,7 @@
         <v>324</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="L43" s="1" t="n">
         <v>0.6</v>
@@ -8797,6 +8797,7 @@
       <c r="H63" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="M63" s="0"/>
       <c r="O63" s="6"/>
       <c r="P63" s="6"/>
       <c r="Q63" s="6"/>
